--- a/docs/files/exports/readme.xlsx
+++ b/docs/files/exports/readme.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>699 words</t>
+          <t>391 words</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/docs/files/exports/readme.xlsx
+++ b/docs/files/exports/readme.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>391 words</t>
+          <t>419 words</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/docs/files/exports/readme.xlsx
+++ b/docs/files/exports/readme.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>419 words</t>
+          <t>277 words</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
